--- a/artfynd/A 39857-2020 artfynd.xlsx
+++ b/artfynd/A 39857-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126420378</v>
       </c>
       <c r="B2" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126420063</v>
       </c>
       <c r="B3" t="n">
-        <v>104277</v>
+        <v>104286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126420367</v>
       </c>
       <c r="B4" t="n">
-        <v>107026</v>
+        <v>107035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
